--- a/iot-web/public/import/meterMachine.xlsx
+++ b/iot-web/public/import/meterMachine.xlsx
@@ -1,22 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12540"/>
+    <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="水电表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
-    <t>有</t>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>表号</t>
+  </si>
+  <si>
+    <t>表类型</t>
+  </si>
+  <si>
+    <t>模式</t>
+  </si>
+  <si>
+    <t>房屋</t>
+  </si>
+  <si>
+    <t>厂家</t>
+  </si>
+  <si>
+    <t>采集器ID</t>
+  </si>
+  <si>
+    <t>1-1-1智能水表</t>
   </si>
   <si>
     <t>说明</t>
@@ -25,47 +46,23 @@
     <t>请一定看下面说明</t>
   </si>
   <si>
-    <t>名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>表号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>表类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>模式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>房屋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>费用项</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>厂家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>采集器ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>智能表名称，推荐为房屋+电表或者水表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>智能表地址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写费用下的抄表类型的名称</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>充值模式为1001
 抄表模式为</t>
     </r>
@@ -74,16 +71,21 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>2002</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>格式为1</t>
     </r>
     <r>
@@ -91,43 +93,33 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>-1-1001</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>费用项名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>拓强电表-单相远程单费率预付费表 为 2
 拓强水表-Lora无预付费水表 为 3
 拓强水表-Lora普通预付费水表 为 4
 拓强电表-单相单费率电表 为 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>表采集器ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1-1-1智能水表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请填写费用下的抄表类型的名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,29 +128,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -194,30 +509,319 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -479,60 +1083,57 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
-    <col min="6" max="7" width="10.75" customWidth="1"/>
-    <col min="13" max="13" width="37.625" customWidth="1"/>
-    <col min="15" max="15" width="22.375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="34.125" customWidth="1"/>
+    <col min="6" max="6" width="10.75" customWidth="1"/>
+    <col min="12" max="12" width="37.625" customWidth="1"/>
+    <col min="14" max="14" width="22.375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="4"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="5"/>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="9" t="s">
-        <v>18</v>
       </c>
       <c r="B2" s="2">
         <v>1212</v>
@@ -546,683 +1147,625 @@
       <c r="E2" s="2">
         <v>33</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="F2" s="2">
         <v>110</v>
       </c>
-      <c r="H2" s="4">
+      <c r="G2" s="3">
         <v>10102</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="5"/>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="4"/>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="5"/>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="4"/>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="G4" s="3"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="5"/>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="4"/>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="G5" s="3"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" t="s">
+        <v>8</v>
+      </c>
       <c r="L5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" t="s">
-        <v>2</v>
-      </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="5"/>
-    </row>
-    <row r="6" spans="1:17">
+        <v>9</v>
+      </c>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="4"/>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="G6" s="3"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="7" t="s">
+        <v>0</v>
+      </c>
       <c r="L6" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="5"/>
-    </row>
-    <row r="7" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="G7" s="3"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="5"/>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="4"/>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="G8" s="3"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="5"/>
-    </row>
-    <row r="9" spans="1:17" ht="28.5">
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="4"/>
+    </row>
+    <row r="9" ht="28.5" spans="1:16">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M9" s="8" t="s">
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="4"/>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="G10" s="3"/>
       <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="L10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="M10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="4"/>
+    </row>
+    <row r="11" ht="57" spans="1:16">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="G11" s="3"/>
       <c r="H11" s="4"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M11" s="7" t="s">
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" ht="57">
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="4"/>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="G12" s="3"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="L12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="M12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="4"/>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="4"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="4"/>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="G14" s="3"/>
       <c r="H14" s="4"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="5"/>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="4"/>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="G15" s="3"/>
       <c r="H15" s="4"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="5"/>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="4"/>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="G16" s="3"/>
       <c r="H16" s="4"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="5"/>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="G17" s="3"/>
       <c r="H17" s="4"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="G18" s="3"/>
       <c r="H18" s="4"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="G19" s="3"/>
       <c r="H19" s="4"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="G20" s="3"/>
       <c r="H20" s="4"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="G21" s="3"/>
       <c r="H21" s="4"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+      <c r="G22" s="3"/>
       <c r="H22" s="4"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="G23" s="3"/>
       <c r="H23" s="4"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+      <c r="G24" s="3"/>
       <c r="H24" s="4"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="G25" s="3"/>
       <c r="H25" s="4"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-    </row>
-    <row r="26" spans="1:17">
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
+      <c r="G26" s="3"/>
       <c r="H26" s="4"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-    </row>
-    <row r="27" spans="1:17">
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+      <c r="G27" s="3"/>
       <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
+      <c r="G28" s="3"/>
       <c r="H28" s="4"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-    </row>
-    <row r="29" spans="1:17">
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
+      <c r="G29" s="3"/>
       <c r="H29" s="4"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
+      <c r="G30" s="3"/>
       <c r="H30" s="4"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-    </row>
-    <row r="31" spans="1:17">
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
+      <c r="G31" s="3"/>
       <c r="H31" s="4"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-    </row>
-    <row r="32" spans="1:17">
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
+      <c r="G32" s="3"/>
       <c r="H32" s="4"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-    </row>
-    <row r="33" spans="1:17">
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
+      <c r="G33" s="3"/>
       <c r="H33" s="4"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-    </row>
-    <row r="34" spans="1:17">
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
+      <c r="G34" s="3"/>
       <c r="H34" s="4"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-    </row>
-    <row r="35" spans="1:17">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="203" verticalDpi="203"/>
+  <headerFooter/>
 </worksheet>
 </file>